--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -461,10 +461,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -546,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -888,9 +888,26 @@
         <v>579.599</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>la planet electrique</v>
+      </c>
+      <c r="B21" t="str">
+        <v xml:space="preserve">matériel électrique et chemin du câble </v>
+      </c>
+      <c r="C21" t="str">
+        <v>824/26</v>
+      </c>
+      <c r="D21" t="str">
+        <v>direct</v>
+      </c>
+      <c r="E21">
+        <v>12000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -960,7 +977,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -990,7 +1007,7 @@
         <v>2026-09-01</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" t="str">
         <v xml:space="preserve">VERS KNAIS POUR LE POINTAGE matériel </v>
@@ -1018,7 +1035,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E4" t="str">
         <v>salah et khaled to etude</v>
@@ -1032,7 +1049,7 @@
         <v>2026-01-10</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E5" t="str">
         <v>salah et khaled to etude</v>
@@ -1046,7 +1063,7 @@
         <v>2026-01-14</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E6" t="str">
         <v>deplacement fourniseurs à tunis: inox pa, tunitaly, ifm le 14/01/2026</v>
@@ -1060,7 +1077,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E7" t="str">
         <v>deplacement fourniseurs à tunis: jets 15/01/2026</v>
@@ -1074,7 +1091,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E8" t="str">
         <v>deplacement fourniseurs à tunis: 16/01/2026 CDR PCM</v>
@@ -1088,7 +1105,7 @@
         <v>2026-01-28</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E9" t="str">
         <v xml:space="preserve">deplacement sidi bouzid: prise des notes </v>
@@ -1192,9 +1209,65 @@
         <v>déplacement cuve omar</v>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="D17">
+        <v>150</v>
+      </c>
+      <c r="E17" t="str">
+        <v>déplacement rafik et khaled clsb</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="D18">
+        <v>140</v>
+      </c>
+      <c r="E18" t="str">
+        <v>déplacement ali to cuve omar</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="D19">
+        <v>140</v>
+      </c>
+      <c r="E19" t="str">
+        <v>déplacement ali to cuve omar</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="D20">
+        <v>140</v>
+      </c>
+      <c r="E20" t="str">
+        <v>déplacement ali to cuve omar</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1337,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1364,7 +1437,7 @@
         <v>ASAM ENGINEERING</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-11-29</v>
+        <v>2026-12-15</v>
       </c>
       <c r="D2" t="str">
         <v>NON_PAYE</v>
@@ -1565,7 +1638,7 @@
         <v>TECHNOPREST</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-11-26</v>
+        <v>2026-11-24</v>
       </c>
       <c r="D14" t="str">
         <v>NON_PAYE</v>
@@ -1575,135 +1648,132 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>PAY-1788959849633-2</v>
-      </c>
       <c r="B15" t="str">
-        <v>TECHNOPREST</v>
+        <v>MASTER MOTION</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-09-10</v>
+        <v>2026-12-30</v>
       </c>
       <c r="D15" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E15">
-        <v>21147.441</v>
+        <v>22250.025</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="str">
-        <v>MASTER MOTION</v>
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-12-30</v>
+        <v>2026-12-21</v>
       </c>
       <c r="D16" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E16">
-        <v>22250.025</v>
+        <v>21289.1</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="str">
+        <v>PAY-1788960332858-1</v>
+      </c>
       <c r="B17" t="str">
-        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+        <v>EQUIPEMENT MODERNE</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-12-15</v>
+        <v>2026-07-08</v>
       </c>
       <c r="D17" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E17">
-        <v>21289.1</v>
+        <v>4719.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>PAY-1788960332858-1</v>
+        <v>PAY-1788960332858-2</v>
       </c>
       <c r="B18" t="str">
         <v>EQUIPEMENT MODERNE</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-07-08</v>
+        <v>2026-09-27</v>
       </c>
       <c r="D18" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E18">
-        <v>4719.49</v>
+        <v>11012.13</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>PAY-1788960332858-2</v>
-      </c>
       <c r="B19" t="str">
-        <v>EQUIPEMENT MODERNE</v>
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-09-16</v>
+        <v>2026-12-21</v>
       </c>
       <c r="D19" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E19">
-        <v>11012.13</v>
+        <v>55123</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="str">
+        <v>PAY-1788961978871-1</v>
+      </c>
       <c r="B20" t="str">
-        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+        <v>GENERAL METAL</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-12-15</v>
+        <v>2026-08-06</v>
       </c>
       <c r="D20" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E20">
-        <v>111360.2</v>
+        <v>6636</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PAY-1788961978871-1</v>
+        <v>PAY-1788961978871-2</v>
       </c>
       <c r="B21" t="str">
         <v>GENERAL METAL</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-08-06</v>
+        <v>2026-10-01</v>
       </c>
       <c r="D21" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E21">
+        <v>6280.672</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>BYMS</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="D22" t="str">
         <v>PAYE</v>
       </c>
-      <c r="E21">
-        <v>6636</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>PAY-1788961978871-2</v>
-      </c>
-      <c r="B22" t="str">
-        <v>GENERAL METAL</v>
-      </c>
-      <c r="C22" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="D22" t="str">
-        <v>NON_PAYE</v>
-      </c>
       <c r="E22">
-        <v>6280.672</v>
+        <v>413.338</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="str">
-        <v>BYMS</v>
+        <v>AMEL</v>
       </c>
       <c r="C23" t="str">
         <v>2026-09-01</v>
@@ -1712,49 +1782,52 @@
         <v>PAYE</v>
       </c>
       <c r="E23">
-        <v>413.338</v>
+        <v>14673.95</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="str">
+        <v>PAY-1788962583498-1</v>
+      </c>
       <c r="B24" t="str">
-        <v>AMEL</v>
+        <v>SOCIETE BIAS</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-23</v>
       </c>
       <c r="D24" t="str">
         <v>PAYE</v>
       </c>
       <c r="E24">
-        <v>14673.95</v>
+        <v>2585.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PAY-1788962583498-1</v>
+        <v>PAY-1788962583498-2</v>
       </c>
       <c r="B25" t="str">
         <v>SOCIETE BIAS</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-07-23</v>
+        <v>2026-08-26</v>
       </c>
       <c r="D25" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E25">
-        <v>2585.12</v>
+        <v>1938.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PAY-1788962583498-2</v>
+        <v>PAY-1788962583498-3</v>
       </c>
       <c r="B26" t="str">
         <v>SOCIETE BIAS</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-08-26</v>
+        <v>2026-09-26</v>
       </c>
       <c r="D26" t="str">
         <v>NON_PAYE</v>
@@ -1764,62 +1837,59 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>PAY-1788962583498-3</v>
-      </c>
       <c r="B27" t="str">
-        <v>SOCIETE BIAS</v>
+        <v>UNIVERS AUTOMATISME</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-09</v>
       </c>
       <c r="D27" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E27">
-        <v>1938.84</v>
+        <v>579.599</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="str">
-        <v>UNIVERS AUTOMATISME</v>
+        <v>LA MAISON DE L'INOX</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-09-09</v>
+        <v>2026-08-31</v>
       </c>
       <c r="D28" t="str">
         <v>PAYE</v>
       </c>
       <c r="E28">
-        <v>579.599</v>
+        <v>34448.093</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="str">
-        <v>LA MAISON DE L'INOX</v>
+        <v>SOCIETE BIAS</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-08-31</v>
+        <v>2026-08-06</v>
       </c>
       <c r="D29" t="str">
         <v>PAYE</v>
       </c>
       <c r="E29">
-        <v>34448.093</v>
+        <v>3801.768</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="str">
-        <v>SOCIETE BIAS</v>
+        <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-08-06</v>
+        <v>2026-09-11</v>
       </c>
       <c r="D30" t="str">
         <v>PAYE</v>
       </c>
       <c r="E30">
-        <v>3801.768</v>
+        <v>4763.262</v>
       </c>
     </row>
     <row r="31">
@@ -1827,32 +1897,88 @@
         <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-09-11</v>
+        <v>2026-10-01</v>
       </c>
       <c r="D31" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E31">
-        <v>4763.262</v>
+        <v>11051.278</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="str">
-        <v>AMF INDUSTRIELLE</v>
+        <v>la planet</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-15</v>
       </c>
       <c r="D32" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <v>TECHNOPREST</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="D33" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E33">
+        <v>14294.252</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="str">
+        <v>TECHNOPREST</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2027-01-14</v>
+      </c>
+      <c r="D34" t="str">
         <v>NON_PAYE</v>
       </c>
-      <c r="E32">
-        <v>11051.278</v>
+      <c r="E34">
+        <v>6139.751</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="str">
+        <v>TECHNOPREST</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="D35" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E35">
+        <v>1316.656</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="str">
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026-12-21</v>
+      </c>
+      <c r="D36" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E36">
+        <v>55123</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -1410,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1662,104 +1662,104 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="str">
+        <v>PAY-1788960332858-1</v>
+      </c>
       <c r="B16" t="str">
-        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+        <v>EQUIPEMENT MODERNE</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-12-21</v>
+        <v>2026-07-08</v>
       </c>
       <c r="D16" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E16">
-        <v>21289.1</v>
+        <v>4719.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>PAY-1788960332858-1</v>
+        <v>PAY-1788960332858-2</v>
       </c>
       <c r="B17" t="str">
         <v>EQUIPEMENT MODERNE</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-07-08</v>
+        <v>2026-09-27</v>
       </c>
       <c r="D17" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E17">
-        <v>4719.49</v>
+        <v>11012.13</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>PAY-1788960332858-2</v>
-      </c>
       <c r="B18" t="str">
-        <v>EQUIPEMENT MODERNE</v>
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-09-27</v>
+        <v>2026-12-21</v>
       </c>
       <c r="D18" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E18">
-        <v>11012.13</v>
+        <v>76200</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="str">
+        <v>PAY-1788961978871-1</v>
+      </c>
       <c r="B19" t="str">
-        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+        <v>GENERAL METAL</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-12-21</v>
+        <v>2026-08-06</v>
       </c>
       <c r="D19" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E19">
-        <v>55123</v>
+        <v>6636</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PAY-1788961978871-1</v>
+        <v>PAY-1788961978871-2</v>
       </c>
       <c r="B20" t="str">
         <v>GENERAL METAL</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-08-06</v>
+        <v>2026-10-01</v>
       </c>
       <c r="D20" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E20">
+        <v>6280.672</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>BYMS</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="D21" t="str">
         <v>PAYE</v>
       </c>
-      <c r="E20">
-        <v>6636</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>PAY-1788961978871-2</v>
-      </c>
-      <c r="B21" t="str">
-        <v>GENERAL METAL</v>
-      </c>
-      <c r="C21" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="D21" t="str">
-        <v>NON_PAYE</v>
-      </c>
       <c r="E21">
-        <v>6280.672</v>
+        <v>413.338</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="str">
-        <v>BYMS</v>
+        <v>AMEL</v>
       </c>
       <c r="C22" t="str">
         <v>2026-09-01</v>
@@ -1768,49 +1768,52 @@
         <v>PAYE</v>
       </c>
       <c r="E22">
-        <v>413.338</v>
+        <v>14673.95</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="str">
+        <v>PAY-1788962583498-1</v>
+      </c>
       <c r="B23" t="str">
-        <v>AMEL</v>
+        <v>SOCIETE BIAS</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-23</v>
       </c>
       <c r="D23" t="str">
         <v>PAYE</v>
       </c>
       <c r="E23">
-        <v>14673.95</v>
+        <v>2585.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>PAY-1788962583498-1</v>
+        <v>PAY-1788962583498-2</v>
       </c>
       <c r="B24" t="str">
         <v>SOCIETE BIAS</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-07-23</v>
+        <v>2026-08-26</v>
       </c>
       <c r="D24" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E24">
-        <v>2585.12</v>
+        <v>1938.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PAY-1788962583498-2</v>
+        <v>PAY-1788962583498-3</v>
       </c>
       <c r="B25" t="str">
         <v>SOCIETE BIAS</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-08-26</v>
+        <v>2026-09-26</v>
       </c>
       <c r="D25" t="str">
         <v>NON_PAYE</v>
@@ -1820,62 +1823,59 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>PAY-1788962583498-3</v>
-      </c>
       <c r="B26" t="str">
-        <v>SOCIETE BIAS</v>
+        <v>UNIVERS AUTOMATISME</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-09</v>
       </c>
       <c r="D26" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E26">
-        <v>1938.84</v>
+        <v>579.599</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="str">
-        <v>UNIVERS AUTOMATISME</v>
+        <v>LA MAISON DE L'INOX</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-09-09</v>
+        <v>2026-08-31</v>
       </c>
       <c r="D27" t="str">
         <v>PAYE</v>
       </c>
       <c r="E27">
-        <v>579.599</v>
+        <v>34448.093</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="str">
-        <v>LA MAISON DE L'INOX</v>
+        <v>SOCIETE BIAS</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-08-31</v>
+        <v>2026-08-06</v>
       </c>
       <c r="D28" t="str">
         <v>PAYE</v>
       </c>
       <c r="E28">
-        <v>34448.093</v>
+        <v>3801.768</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="str">
-        <v>SOCIETE BIAS</v>
+        <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-08-06</v>
+        <v>2026-09-11</v>
       </c>
       <c r="D29" t="str">
         <v>PAYE</v>
       </c>
       <c r="E29">
-        <v>3801.768</v>
+        <v>4763.262</v>
       </c>
     </row>
     <row r="30">
@@ -1883,41 +1883,41 @@
         <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-09-11</v>
+        <v>2026-10-01</v>
       </c>
       <c r="D30" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E30">
-        <v>4763.262</v>
+        <v>11051.278</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="str">
-        <v>AMF INDUSTRIELLE</v>
+        <v>la planet</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-15</v>
       </c>
       <c r="D31" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E31">
-        <v>11051.278</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="str">
-        <v>la planet</v>
+        <v>TECHNOPREST</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-09-15</v>
+        <v>2026-08-14</v>
       </c>
       <c r="D32" t="str">
         <v>PAYE</v>
       </c>
       <c r="E32">
-        <v>3000</v>
+        <v>14294.252</v>
       </c>
     </row>
     <row r="33">
@@ -1925,13 +1925,13 @@
         <v>TECHNOPREST</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-08-14</v>
+        <v>2027-01-14</v>
       </c>
       <c r="D33" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E33">
-        <v>14294.252</v>
+        <v>6139.751</v>
       </c>
     </row>
     <row r="34">
@@ -1939,46 +1939,32 @@
         <v>TECHNOPREST</v>
       </c>
       <c r="C34" t="str">
-        <v>2027-01-14</v>
+        <v>2026-09-18</v>
       </c>
       <c r="D34" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E34">
-        <v>6139.751</v>
+        <v>1316.656</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="str">
-        <v>TECHNOPREST</v>
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-09-18</v>
+        <v>2027-01-21</v>
       </c>
       <c r="D35" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E35">
-        <v>1316.656</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="str">
-        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
-      </c>
-      <c r="C36" t="str">
-        <v>2026-12-21</v>
-      </c>
-      <c r="D36" t="str">
-        <v>NON_PAYE</v>
-      </c>
-      <c r="E36">
         <v>55123</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E35"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -461,10 +461,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I2">
         <v>0</v>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -461,10 +461,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -546,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -893,7 +893,7 @@
         <v>la planet electrique</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">matériel électrique et chemin du câble </v>
+        <v xml:space="preserve">matériel électrique sans chemin      -- chemin du câble  du cable </v>
       </c>
       <c r="C21" t="str">
         <v>824/26</v>
@@ -902,12 +902,46 @@
         <v>direct</v>
       </c>
       <c r="E21">
-        <v>12000</v>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>la planet electrique</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>890/26</v>
+      </c>
+      <c r="D22" t="str">
+        <v>direct</v>
+      </c>
+      <c r="E22">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>ste habachi</v>
+      </c>
+      <c r="B23" t="str">
+        <v>cosse embou double 0.75</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-3187</v>
+      </c>
+      <c r="D23" t="str">
+        <v>direct</v>
+      </c>
+      <c r="E23">
+        <v>32.059</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -977,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1265,9 +1299,23 @@
         <v>déplacement ali to cuve omar</v>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-10-10</v>
+      </c>
+      <c r="D21">
+        <v>980</v>
+      </c>
+      <c r="E21" t="str">
+        <v>déplacement ali to cuve omar 7 jour</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2065,16 +2113,16 @@
         <v>126</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F4" t="str">
-        <v>EN_COURS</v>
+        <v>EN_AVANCE</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2026-10-20</v>
       </c>
       <c r="H4">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -2126,7 +2174,7 @@
         <v/>
       </c>
       <c r="H6">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -461,10 +461,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H2">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1011,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1313,9 +1313,23 @@
         <v>déplacement ali to cuve omar 7 jour</v>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="D22">
+        <v>150</v>
+      </c>
+      <c r="E22" t="str">
+        <v>déplacement rochdi cuve omar 100 dt  5 jours gazoil et sandwich</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1386,13 +1400,13 @@
         <v>rochdi</v>
       </c>
       <c r="C4" t="str">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>155</v>
       </c>
       <c r="E4">
-        <v>1240</v>
+        <v>2325</v>
       </c>
       <c r="F4" t="str">
         <v xml:space="preserve">Project mangement &amp; développement </v>
@@ -1403,13 +1417,13 @@
         <v xml:space="preserve">sondes </v>
       </c>
       <c r="C5" t="str">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <v>29</v>
       </c>
       <c r="E5">
-        <v>435</v>
+        <v>1740</v>
       </c>
       <c r="F5" t="str">
         <v>achat</v>
@@ -1420,13 +1434,13 @@
         <v>faten</v>
       </c>
       <c r="C6" t="str">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D6">
         <v>29</v>
       </c>
       <c r="E6">
-        <v>435</v>
+        <v>1740</v>
       </c>
       <c r="F6" t="str">
         <v>achat</v>
@@ -1458,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1519,13 +1533,13 @@
         <v>SIMS</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-11-29</v>
+        <v>2026-12-12</v>
       </c>
       <c r="D4" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E4">
-        <v>19134.25</v>
+        <v>10114.988</v>
       </c>
     </row>
     <row r="5">
@@ -1536,7 +1550,7 @@
         <v>SIMS</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-12-29</v>
+        <v>2027-01-12</v>
       </c>
       <c r="D5" t="str">
         <v>NON_PAYE</v>
@@ -1570,13 +1584,13 @@
         <v>TUNISIE INOX</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-12-21</v>
+        <v>2027-01-13</v>
       </c>
       <c r="D7" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E7">
-        <v>38175.2</v>
+        <v>74221.3</v>
       </c>
     </row>
     <row r="8">
@@ -1587,13 +1601,13 @@
         <v>TUNISIE INOX</v>
       </c>
       <c r="C8" t="str">
-        <v>2027-01-21</v>
+        <v>2027-01-13</v>
       </c>
       <c r="D8" t="str">
         <v>NON_PAYE</v>
       </c>
       <c r="E8">
-        <v>95438</v>
+        <v>10226.908</v>
       </c>
     </row>
     <row r="9">
@@ -1737,7 +1751,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="D17" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E17">
         <v>11012.13</v>
@@ -1785,7 +1799,7 @@
         <v>2026-10-01</v>
       </c>
       <c r="D20" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E20">
         <v>6280.672</v>
@@ -1864,7 +1878,7 @@
         <v>2026-09-26</v>
       </c>
       <c r="D25" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E25">
         <v>1938.84</v>
@@ -1934,7 +1948,7 @@
         <v>2026-10-01</v>
       </c>
       <c r="D30" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E30">
         <v>11051.278</v>
@@ -2010,9 +2024,23 @@
         <v>55123</v>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="str">
+        <v>SIMS</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="D36" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E36">
+        <v>10114.988</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -41,12 +41,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -461,10 +457,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I2">
         <v>0</v>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -457,10 +457,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -889,7 +889,7 @@
         <v>la planet electrique</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">matériel électrique sans chemin      -- chemin du câble  du cable </v>
+        <v xml:space="preserve">matériel électrique sans chemin      -- chemin du câble </v>
       </c>
       <c r="C21" t="str">
         <v>824/26</v>
@@ -935,9 +935,43 @@
         <v>32.059</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>hbc</v>
+      </c>
+      <c r="B24" t="str">
+        <v>clapet et soupape et casse vide</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>41</v>
+      </c>
+      <c r="E24">
+        <v>2217.366</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>MAISON INOX</v>
+      </c>
+      <c r="B25" t="str">
+        <v xml:space="preserve">raccord din </v>
+      </c>
+      <c r="C25" t="str">
+        <v>-</v>
+      </c>
+      <c r="D25" t="str">
+        <v>dj8567</v>
+      </c>
+      <c r="E25">
+        <v>258.42</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1379,13 +1413,13 @@
         <v>MR khaled</v>
       </c>
       <c r="C3" t="str">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>200</v>
       </c>
       <c r="E3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="F3" t="str">
         <v xml:space="preserve">développement &amp; chef des équipe </v>
@@ -1396,13 +1430,13 @@
         <v>rochdi</v>
       </c>
       <c r="C4" t="str">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D4">
         <v>155</v>
       </c>
       <c r="E4">
-        <v>2325</v>
+        <v>18600</v>
       </c>
       <c r="F4" t="str">
         <v xml:space="preserve">Project mangement &amp; développement </v>
@@ -1413,13 +1447,13 @@
         <v xml:space="preserve">sondes </v>
       </c>
       <c r="C5" t="str">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>29</v>
       </c>
       <c r="E5">
-        <v>1740</v>
+        <v>2610</v>
       </c>
       <c r="F5" t="str">
         <v>achat</v>
@@ -1430,13 +1464,13 @@
         <v>faten</v>
       </c>
       <c r="C6" t="str">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>29</v>
       </c>
       <c r="E6">
-        <v>1740</v>
+        <v>2610</v>
       </c>
       <c r="F6" t="str">
         <v>achat</v>
@@ -1447,13 +1481,13 @@
         <v>manel</v>
       </c>
       <c r="C7" t="str">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>58</v>
       </c>
       <c r="E7">
-        <v>1160</v>
+        <v>2320</v>
       </c>
       <c r="F7" t="str">
         <v>achat</v>
@@ -1468,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2034,16 +2068,58 @@
         <v>10114.988</v>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="str">
+        <v>MAISON INOX</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D37" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E37">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="str">
+        <v>hbc</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026-11-23</v>
+      </c>
+      <c r="D38" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="str">
+        <v>hbc</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D39" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E39">
+        <v>1195.202</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2163,16 +2239,16 @@
         <v>71</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>EN_COURS</v>
+        <v>EN_AVANCE</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2026-10-03</v>
       </c>
       <c r="H5">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -2192,105 +2268,105 @@
         <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>A_VENIR</v>
+        <v>EN_COURS</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve"> Montage &amp; FAT</v>
+        <v>Fabrication 2 tanks</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-11-10</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-11-30</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="F7" t="str">
-        <v>A_VENIR</v>
+        <v>EN_RETARD</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Installation &amp; câblage</v>
+        <v>câblages des armoires électriques</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-11-30</v>
+        <v>2026-09-01</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-12-11</v>
+        <v>2026-11-20</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>A_VENIR</v>
+        <v>EN_COURS</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mise en service &amp; tests</v>
+        <v xml:space="preserve"> Montage 2 skid &amp; fat</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-12-11</v>
+        <v>2026-10-12</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-12-15</v>
+        <v>2026-11-30</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="str">
-        <v>A_VENIR</v>
+        <v>EN_COURS</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Réception projet</v>
+        <v>Installation &amp; câblage</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-12-15</v>
+        <v>2026-11-30</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-12-15</v>
+        <v>2026-12-11</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2302,12 +2378,64 @@
         <v/>
       </c>
       <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Mise en service &amp; tests</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-12-11</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <v>A_VENIR</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Réception projet</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <v>A_VENIR</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -457,10 +457,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1502,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2110,9 +2110,23 @@
         <v>1195.202</v>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="str">
+        <v>lin</v>
+      </c>
+      <c r="C40" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D40" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E40">
+        <v>409</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E40"/>
   </ignoredErrors>
 </worksheet>
 </file>
